--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E448D064-AE5C-4C8C-B9E3-276BE22D62D2}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE3AB20-0AC9-46B7-946B-A21C70160C2A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3739,25 +3739,47 @@
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
+      <c r="A63" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B63" s="9">
+        <v>450</v>
+      </c>
+      <c r="C63" s="9">
+        <v>60</v>
+      </c>
+      <c r="D63" s="9">
+        <v>100</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>480</v>
+      </c>
+      <c r="I63" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
+        <v>350</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE3AB20-0AC9-46B7-946B-A21C70160C2A}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDE0F66D-E293-4843-A9DC-745F199D8EE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3783,26 +3783,50 @@
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
+      <c r="A64" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B64" s="9">
+        <v>400</v>
+      </c>
+      <c r="C64" s="9">
+        <v>60</v>
+      </c>
+      <c r="D64" s="9">
+        <v>420</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>420</v>
+      </c>
+      <c r="I64" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDE0F66D-E293-4843-A9DC-745F199D8EE3}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DF819E-40D3-4690-BB64-BAB238D2C249}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>studied c++  for mid term</t>
+  </si>
+  <si>
+    <t>exams</t>
   </si>
 </sst>
 </file>
@@ -3829,26 +3832,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+      <c r="A65" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B65" s="9">
+        <v>450</v>
+      </c>
+      <c r="C65" s="9">
+        <v>60</v>
+      </c>
+      <c r="D65" s="9">
+        <v>480</v>
+      </c>
+      <c r="E65" s="9">
+        <v>30</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>360</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DF819E-40D3-4690-BB64-BAB238D2C249}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C4BB389-3C22-4889-A3B1-9F1B1529E144}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>exams</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -3878,26 +3884,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+      <c r="A66" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B66" s="9">
+        <v>450</v>
+      </c>
+      <c r="C66" s="9">
+        <v>60</v>
+      </c>
+      <c r="D66" s="9">
+        <v>480</v>
+      </c>
+      <c r="E66" s="9">
+        <v>60</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>360</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C4BB389-3C22-4889-A3B1-9F1B1529E144}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7A421E9-5FF2-471E-A894-1FAA503BCDA3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3930,26 +3930,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+      <c r="A67" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B67" s="9">
+        <v>400</v>
+      </c>
+      <c r="C67" s="9">
+        <v>60</v>
+      </c>
+      <c r="D67" s="9">
+        <v>480</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>420</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
+        <v>80</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7A421E9-5FF2-471E-A894-1FAA503BCDA3}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D41E03C-9E17-48EA-ACE4-1EBD425444C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3976,26 +3976,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+      <c r="A68" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B68" s="9">
+        <v>400</v>
+      </c>
+      <c r="C68" s="9">
+        <v>60</v>
+      </c>
+      <c r="D68" s="9">
+        <v>480</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>360</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D41E03C-9E17-48EA-ACE4-1EBD425444C9}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B3E1C9-8D56-4F91-9884-73F0C9270A1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4022,26 +4022,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+      <c r="A69" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B69" s="9">
+        <v>400</v>
+      </c>
+      <c r="C69" s="9">
+        <v>60</v>
+      </c>
+      <c r="D69" s="9">
+        <v>480</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0</v>
+      </c>
+      <c r="G69" s="9">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9">
+        <v>360</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B3E1C9-8D56-4F91-9884-73F0C9270A1A}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5887FD1F-0AEB-4B67-854C-D677D2BB6B47}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stressed , don’t know the reason </t>
   </si>
 </sst>
 </file>
@@ -4068,26 +4071,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+      <c r="A70" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B70" s="9">
+        <v>450</v>
+      </c>
+      <c r="C70" s="9">
+        <v>60</v>
+      </c>
+      <c r="D70" s="9">
+        <v>180</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>360</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5887FD1F-0AEB-4B67-854C-D677D2BB6B47}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515FBA2C-149B-4A74-BD51-507A1F389BD3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4117,25 +4117,47 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="A71" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B71" s="9">
+        <v>450</v>
+      </c>
+      <c r="C71" s="9">
+        <v>60</v>
+      </c>
+      <c r="D71" s="9">
+        <v>0</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>420</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
+        <v>510</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515FBA2C-149B-4A74-BD51-507A1F389BD3}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454BC5DE-B782-48EB-B272-EE0A336C9514}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4161,25 +4161,47 @@
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="A72" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B72" s="9">
+        <v>450</v>
+      </c>
+      <c r="C72" s="9">
+        <v>60</v>
+      </c>
+      <c r="D72" s="9">
+        <v>60</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0</v>
+      </c>
+      <c r="F72" s="9">
+        <v>200</v>
+      </c>
+      <c r="G72" s="9">
+        <v>4</v>
+      </c>
+      <c r="H72" s="9">
+        <v>360</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
+        <v>310</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454BC5DE-B782-48EB-B272-EE0A336C9514}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8E9C85-D792-49C7-87E0-74E75CF91A2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4205,25 +4205,47 @@
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+      <c r="A73" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B73" s="9">
+        <v>450</v>
+      </c>
+      <c r="C73" s="9">
+        <v>60</v>
+      </c>
+      <c r="D73" s="9">
+        <v>20</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0</v>
+      </c>
+      <c r="F73" s="9">
+        <v>0</v>
+      </c>
+      <c r="G73" s="9">
+        <v>0</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>530</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
+        <v>910</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8E9C85-D792-49C7-87E0-74E75CF91A2F}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F92C33-BE2E-431C-826D-E7EC0CF91D78}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4227,15 +4227,15 @@
         <v>0</v>
       </c>
       <c r="H73" s="9">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v>530</v>
+        <v>950</v>
       </c>
       <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v>910</v>
+        <v>490</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>54</v>
@@ -4249,25 +4249,47 @@
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+      <c r="A74" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B74" s="9">
+        <v>450</v>
+      </c>
+      <c r="C74" s="9">
+        <v>60</v>
+      </c>
+      <c r="D74" s="9">
+        <v>120</v>
+      </c>
+      <c r="E74" s="9">
+        <v>50</v>
+      </c>
+      <c r="F74" s="9">
+        <v>250</v>
+      </c>
+      <c r="G74" s="9">
+        <v>5</v>
+      </c>
+      <c r="H74" s="9">
+        <v>180</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
+        <v>330</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F92C33-BE2E-431C-826D-E7EC0CF91D78}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41418F31-7344-4907-BDA7-4C96A8AEDD4C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4293,25 +4293,47 @@
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="A75" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B75" s="9">
+        <v>450</v>
+      </c>
+      <c r="C75" s="9">
+        <v>60</v>
+      </c>
+      <c r="D75" s="9">
+        <v>180</v>
+      </c>
+      <c r="E75" s="9">
+        <v>20</v>
+      </c>
+      <c r="F75" s="9">
+        <v>300</v>
+      </c>
+      <c r="G75" s="9">
+        <v>6</v>
+      </c>
+      <c r="H75" s="9">
+        <v>360</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41418F31-7344-4907-BDA7-4C96A8AEDD4C}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B910DD14-9667-4BDC-86BC-F0181A30C6B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4337,25 +4337,47 @@
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="A76" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B76" s="9">
+        <v>450</v>
+      </c>
+      <c r="C76" s="9">
+        <v>60</v>
+      </c>
+      <c r="D76" s="9">
+        <v>120</v>
+      </c>
+      <c r="E76" s="9">
+        <v>60</v>
+      </c>
+      <c r="F76" s="9">
+        <v>350</v>
+      </c>
+      <c r="G76" s="9">
+        <v>7</v>
+      </c>
+      <c r="H76" s="9">
+        <v>360</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B910DD14-9667-4BDC-86BC-F0181A30C6B9}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92871524-2407-45E5-BC2E-7E14EE9E5EDD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4381,25 +4381,47 @@
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="A77" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B77" s="9">
+        <v>450</v>
+      </c>
+      <c r="C77" s="9">
+        <v>60</v>
+      </c>
+      <c r="D77" s="9">
+        <v>120</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>420</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
+        <v>390</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92871524-2407-45E5-BC2E-7E14EE9E5EDD}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1F71F99-9293-4A7F-82A6-8DC807FA5905}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t xml:space="preserve">stressed , don’t know the reason </t>
+  </si>
+  <si>
+    <t>feeling too sleepy while studying ,but I didn't loose confidence and studied.</t>
   </si>
 </sst>
 </file>
@@ -4424,27 +4427,51 @@
       </c>
       <c r="N77" s="12"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+    <row r="78" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B78" s="9">
+        <v>450</v>
+      </c>
+      <c r="C78" s="9">
+        <v>60</v>
+      </c>
+      <c r="D78" s="9">
+        <v>240</v>
+      </c>
+      <c r="E78" s="9">
+        <v>20</v>
+      </c>
+      <c r="F78" s="9">
+        <v>0</v>
+      </c>
+      <c r="G78" s="9">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9">
+        <v>360</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1F71F99-9293-4A7F-82A6-8DC807FA5905}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A1A23E8-6B5E-471C-9747-3765595FC3D3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4474,25 +4474,47 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="A79" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B79" s="9">
+        <v>450</v>
+      </c>
+      <c r="C79" s="9">
+        <v>60</v>
+      </c>
+      <c r="D79" s="9">
+        <v>240</v>
+      </c>
+      <c r="E79" s="9">
+        <v>50</v>
+      </c>
+      <c r="F79" s="9">
+        <v>0</v>
+      </c>
+      <c r="G79" s="9">
+        <v>0</v>
+      </c>
+      <c r="H79" s="9">
+        <v>420</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
+        <v>220</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A1A23E8-6B5E-471C-9747-3765595FC3D3}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6FFA669-F7B1-4FF0-B7B6-4AD211EF0223}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4496,15 +4496,15 @@
         <v>0</v>
       </c>
       <c r="H79" s="9">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="K79" s="11" t="s">
         <v>54</v>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="321" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6FFA669-F7B1-4FF0-B7B6-4AD211EF0223}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00D35475-9A86-4E2D-869F-CAEF907CFFEE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4518,25 +4518,47 @@
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="A80" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B80" s="9">
+        <v>450</v>
+      </c>
+      <c r="C80" s="9">
+        <v>60</v>
+      </c>
+      <c r="D80" s="9">
+        <v>240</v>
+      </c>
+      <c r="E80" s="9">
+        <v>20</v>
+      </c>
+      <c r="F80" s="9">
+        <v>250</v>
+      </c>
+      <c r="G80" s="9">
+        <v>5</v>
+      </c>
+      <c r="H80" s="9">
+        <v>360</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
+        <v>60</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00D35475-9A86-4E2D-869F-CAEF907CFFEE}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE75F6F2-D349-4E8B-BC47-EAE47189D809}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4562,25 +4562,47 @@
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
+      <c r="A81" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B81" s="9">
+        <v>450</v>
+      </c>
+      <c r="C81" s="9">
+        <v>60</v>
+      </c>
+      <c r="D81" s="9">
+        <v>240</v>
+      </c>
+      <c r="E81" s="9">
+        <v>50</v>
+      </c>
+      <c r="F81" s="9">
+        <v>200</v>
+      </c>
+      <c r="G81" s="9">
+        <v>4</v>
+      </c>
+      <c r="H81" s="9">
+        <v>420</v>
+      </c>
+      <c r="I81" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J81" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="345" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE75F6F2-D349-4E8B-BC47-EAE47189D809}"/>
+  <xr:revisionPtr revIDLastSave="359" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13CB7821-5CD1-4D8A-A873-C618108894A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4606,25 +4606,47 @@
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10" t="str">
+      <c r="A82" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B82" s="9">
+        <v>450</v>
+      </c>
+      <c r="C82" s="9">
+        <v>60</v>
+      </c>
+      <c r="D82" s="9">
+        <v>240</v>
+      </c>
+      <c r="E82" s="9">
+        <v>30</v>
+      </c>
+      <c r="F82" s="9">
+        <v>300</v>
+      </c>
+      <c r="G82" s="9">
+        <v>6</v>
+      </c>
+      <c r="H82" s="9">
+        <v>180</v>
+      </c>
+      <c r="I82" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="10" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J82" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
+        <v>180</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="359" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13CB7821-5CD1-4D8A-A873-C618108894A4}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65784102-B56C-4694-B8AD-C24919315B42}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4650,25 +4650,47 @@
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10" t="str">
+      <c r="A83" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B83" s="9">
+        <v>450</v>
+      </c>
+      <c r="C83" s="9">
+        <v>60</v>
+      </c>
+      <c r="D83" s="9">
+        <v>120</v>
+      </c>
+      <c r="E83" s="9">
+        <v>30</v>
+      </c>
+      <c r="F83" s="9">
+        <v>350</v>
+      </c>
+      <c r="G83" s="9">
+        <v>7</v>
+      </c>
+      <c r="H83" s="9">
+        <v>360</v>
+      </c>
+      <c r="I83" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J83" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
